--- a/exports/performance_run_1000000.xlsx
+++ b/exports/performance_run_1000000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>52.687</v>
+        <v>48.675</v>
       </c>
       <c r="E2" t="n">
-        <v>57.711</v>
+        <v>52.221</v>
       </c>
       <c r="F2" t="n">
-        <v>52.919</v>
+        <v>49.294</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1163340</v>
+        <v>1164960</v>
       </c>
     </row>
     <row r="3">
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>72.29000000000001</v>
+        <v>71.518</v>
       </c>
       <c r="E3" t="n">
-        <v>74.825</v>
+        <v>74.989</v>
       </c>
       <c r="F3" t="n">
-        <v>72.586</v>
+        <v>71.988</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1154550</v>
+        <v>1157790</v>
       </c>
     </row>
     <row r="4">
@@ -545,19 +545,19 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.058</v>
+        <v>0.057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.079</v>
+        <v>0.082</v>
       </c>
       <c r="F4" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>630</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5">
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>415.963</v>
+        <v>398.48</v>
       </c>
       <c r="E5" t="n">
-        <v>423.589</v>
+        <v>416.651</v>
       </c>
       <c r="F5" t="n">
-        <v>416.602</v>
+        <v>400.943</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>97.515</v>
+        <v>96.619</v>
       </c>
       <c r="E6" t="n">
-        <v>100.115</v>
+        <v>99.919</v>
       </c>
       <c r="F6" t="n">
-        <v>97.828</v>
+        <v>97.39400000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2081280</v>
+        <v>2084790</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>230.987</v>
+        <v>227.287</v>
       </c>
       <c r="E7" t="n">
-        <v>235.305</v>
+        <v>236.768</v>
       </c>
       <c r="F7" t="n">
-        <v>230.634</v>
+        <v>227.051</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2738790</v>
+        <v>2739030</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>953.463</v>
+        <v>869.932</v>
       </c>
       <c r="E8" t="n">
-        <v>1046.154</v>
+        <v>892.433</v>
       </c>
       <c r="F8" t="n">
-        <v>957.581</v>
+        <v>872.615</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>65.3</v>
+        <v>63.849</v>
       </c>
       <c r="E9" t="n">
-        <v>66.65600000000001</v>
+        <v>67.194</v>
       </c>
       <c r="F9" t="n">
-        <v>65.437</v>
+        <v>64.15300000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1159440</v>
+        <v>1160280</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>43.098</v>
+        <v>40.705</v>
       </c>
       <c r="E10" t="n">
-        <v>43.715</v>
+        <v>41.876</v>
       </c>
       <c r="F10" t="n">
-        <v>43.017</v>
+        <v>40.771</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1159620</v>
+        <v>1160520</v>
       </c>
     </row>
     <row r="11">
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>583.615</v>
+        <v>554.77</v>
       </c>
       <c r="E11" t="n">
-        <v>694.881</v>
+        <v>563.467</v>
       </c>
       <c r="F11" t="n">
-        <v>601.6799999999999</v>
+        <v>554.712</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5002980</v>
+        <v>5048400</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>684.367</v>
+        <v>489.635</v>
       </c>
       <c r="E12" t="n">
-        <v>799.193</v>
+        <v>513.102</v>
       </c>
       <c r="F12" t="n">
-        <v>695.803</v>
+        <v>492.871</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>486.934</v>
+        <v>477.902</v>
       </c>
       <c r="E13" t="n">
-        <v>501.223</v>
+        <v>506.108</v>
       </c>
       <c r="F13" t="n">
-        <v>487.411</v>
+        <v>482.014</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>415.424</v>
+        <v>411.024</v>
       </c>
       <c r="E14" t="n">
-        <v>424.233</v>
+        <v>420.021</v>
       </c>
       <c r="F14" t="n">
-        <v>416.235</v>
+        <v>412.102</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1068.874</v>
+        <v>1043.416</v>
       </c>
       <c r="E15" t="n">
-        <v>1162.04</v>
+        <v>1069.192</v>
       </c>
       <c r="F15" t="n">
-        <v>1080.882</v>
+        <v>1045.385</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>979.0599999999999</v>
+        <v>720.1660000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>993.097</v>
+        <v>741.549</v>
       </c>
       <c r="F16" t="n">
-        <v>979.5309999999999</v>
+        <v>722.984</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>642.169</v>
+        <v>599.582</v>
       </c>
       <c r="E17" t="n">
-        <v>659.5069999999999</v>
+        <v>630.758</v>
       </c>
       <c r="F17" t="n">
-        <v>642.8920000000001</v>
+        <v>603.755</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>885.313</v>
+        <v>863.325</v>
       </c>
       <c r="E18" t="n">
-        <v>1081.009</v>
+        <v>871.831</v>
       </c>
       <c r="F18" t="n">
-        <v>925.263</v>
+        <v>829.942</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>483.195</v>
+        <v>471.481</v>
       </c>
       <c r="E19" t="n">
-        <v>533.006</v>
+        <v>481.848</v>
       </c>
       <c r="F19" t="n">
-        <v>491.253</v>
+        <v>472.639</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>499.244</v>
+        <v>453.844</v>
       </c>
       <c r="E20" t="n">
-        <v>523.429</v>
+        <v>469.714</v>
       </c>
       <c r="F20" t="n">
-        <v>501.298</v>
+        <v>455.228</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>780.107</v>
+        <v>719.9109999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>854.4640000000001</v>
+        <v>742.092</v>
       </c>
       <c r="F21" t="n">
-        <v>795.3579999999999</v>
+        <v>722.961</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>42.955</v>
+        <v>39.831</v>
       </c>
       <c r="E22" t="n">
-        <v>46.245</v>
+        <v>42.551</v>
       </c>
       <c r="F22" t="n">
-        <v>43.238</v>
+        <v>40.1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1159920</v>
+        <v>1160730</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>53.215</v>
+        <v>53.359</v>
       </c>
       <c r="E23" t="n">
-        <v>55.075</v>
+        <v>56.113</v>
       </c>
       <c r="F23" t="n">
-        <v>53.422</v>
+        <v>53.84</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1148520</v>
+        <v>1152030</v>
       </c>
     </row>
     <row r="24">
@@ -1145,13 +1145,13 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.047</v>
+        <v>0.054</v>
       </c>
       <c r="E24" t="n">
-        <v>0.051</v>
+        <v>0.081</v>
       </c>
       <c r="F24" t="n">
-        <v>0.049</v>
+        <v>0.057</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>226.11</v>
+        <v>224.516</v>
       </c>
       <c r="E25" t="n">
-        <v>233.705</v>
+        <v>234.457</v>
       </c>
       <c r="F25" t="n">
-        <v>227.172</v>
+        <v>225.897</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1568550</v>
+        <v>1568400</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>64.76000000000001</v>
+        <v>65.032</v>
       </c>
       <c r="E26" t="n">
-        <v>66.639</v>
+        <v>66.727</v>
       </c>
       <c r="F26" t="n">
-        <v>64.884</v>
+        <v>65.274</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1279590</v>
+        <v>1282740</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>110.058</v>
+        <v>102.162</v>
       </c>
       <c r="E27" t="n">
-        <v>113.045</v>
+        <v>126.878</v>
       </c>
       <c r="F27" t="n">
-        <v>110.395</v>
+        <v>105.944</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1437750</v>
+        <v>1435890</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>398.361</v>
+        <v>433.247</v>
       </c>
       <c r="E28" t="n">
-        <v>420.947</v>
+        <v>452.388</v>
       </c>
       <c r="F28" t="n">
-        <v>399.981</v>
+        <v>435.992</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>47.677</v>
+        <v>53.933</v>
       </c>
       <c r="E29" t="n">
-        <v>51.6</v>
+        <v>55.467</v>
       </c>
       <c r="F29" t="n">
-        <v>48.283</v>
+        <v>54.072</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1153410</v>
+        <v>1154520</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>50.255</v>
+        <v>50.642</v>
       </c>
       <c r="E30" t="n">
-        <v>56.398</v>
+        <v>56.406</v>
       </c>
       <c r="F30" t="n">
-        <v>50.531</v>
+        <v>52.26</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1153320</v>
+        <v>1154490</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>172.223</v>
+        <v>313.826</v>
       </c>
       <c r="E31" t="n">
-        <v>187.773</v>
+        <v>323.985</v>
       </c>
       <c r="F31" t="n">
-        <v>174.259</v>
+        <v>314.315</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1561170</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>186.55</v>
+        <v>168.352</v>
       </c>
       <c r="E32" t="n">
-        <v>211.236</v>
+        <v>182.424</v>
       </c>
       <c r="F32" t="n">
-        <v>189.047</v>
+        <v>170.274</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>312.533</v>
+        <v>292.857</v>
       </c>
       <c r="E33" t="n">
-        <v>329.681</v>
+        <v>313.145</v>
       </c>
       <c r="F33" t="n">
-        <v>313.925</v>
+        <v>296.226</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>166.838</v>
+        <v>159.578</v>
       </c>
       <c r="E34" t="n">
-        <v>184.677</v>
+        <v>168.5</v>
       </c>
       <c r="F34" t="n">
-        <v>168.576</v>
+        <v>160.99</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>642.14</v>
+        <v>638.96</v>
       </c>
       <c r="E35" t="n">
-        <v>669.463</v>
+        <v>670.526</v>
       </c>
       <c r="F35" t="n">
-        <v>645.4640000000001</v>
+        <v>641.42</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>197.999</v>
+        <v>183.382</v>
       </c>
       <c r="E36" t="n">
-        <v>222.16</v>
+        <v>230.664</v>
       </c>
       <c r="F36" t="n">
-        <v>198.245</v>
+        <v>191.445</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>397.973</v>
+        <v>340.09</v>
       </c>
       <c r="E37" t="n">
-        <v>479.24</v>
+        <v>384.87</v>
       </c>
       <c r="F37" t="n">
-        <v>410.788</v>
+        <v>351.465</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>415.823</v>
+        <v>453.914</v>
       </c>
       <c r="E38" t="n">
-        <v>442.751</v>
+        <v>491.039</v>
       </c>
       <c r="F38" t="n">
-        <v>418.248</v>
+        <v>458.022</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>277.043</v>
+        <v>238.012</v>
       </c>
       <c r="E39" t="n">
-        <v>299.588</v>
+        <v>280.246</v>
       </c>
       <c r="F39" t="n">
-        <v>280.311</v>
+        <v>244.599</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>317.453</v>
+        <v>307.154</v>
       </c>
       <c r="E40" t="n">
-        <v>339.938</v>
+        <v>323.534</v>
       </c>
       <c r="F40" t="n">
-        <v>319.775</v>
+        <v>309.884</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>336.622</v>
+        <v>325.346</v>
       </c>
       <c r="E41" t="n">
-        <v>389.942</v>
+        <v>338.206</v>
       </c>
       <c r="F41" t="n">
-        <v>344.965</v>
+        <v>326.356</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1548390</v>
+        <v>1548570</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_1000000.xlsx
+++ b/exports/performance_run_1000000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>48.675</v>
+        <v>48.954</v>
       </c>
       <c r="E2" t="n">
-        <v>52.221</v>
+        <v>51.938</v>
       </c>
       <c r="F2" t="n">
-        <v>49.294</v>
+        <v>49.489</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1164960</v>
+        <v>1165020</v>
       </c>
     </row>
     <row r="3">
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>71.518</v>
+        <v>82.562</v>
       </c>
       <c r="E3" t="n">
-        <v>74.989</v>
+        <v>84.27</v>
       </c>
       <c r="F3" t="n">
-        <v>71.988</v>
+        <v>82.67400000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1157790</v>
+        <v>1154760</v>
       </c>
     </row>
     <row r="4">
@@ -548,10 +548,10 @@
         <v>0.057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.082</v>
+        <v>0.076</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,19 +575,19 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>398.48</v>
+        <v>394.306</v>
       </c>
       <c r="E5" t="n">
-        <v>416.651</v>
+        <v>411.085</v>
       </c>
       <c r="F5" t="n">
-        <v>400.943</v>
+        <v>396.667</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5013600</v>
+        <v>5006220</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>96.619</v>
+        <v>96.364</v>
       </c>
       <c r="E6" t="n">
-        <v>99.919</v>
+        <v>98.471</v>
       </c>
       <c r="F6" t="n">
-        <v>97.39400000000001</v>
+        <v>96.676</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2084790</v>
+        <v>2086500</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>227.287</v>
+        <v>220.744</v>
       </c>
       <c r="E7" t="n">
-        <v>236.768</v>
+        <v>231.107</v>
       </c>
       <c r="F7" t="n">
-        <v>227.051</v>
+        <v>222.163</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2739030</v>
+        <v>2730450</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>869.932</v>
+        <v>873.7859999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>892.433</v>
+        <v>900.72</v>
       </c>
       <c r="F8" t="n">
-        <v>872.615</v>
+        <v>877.5839999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>63.849</v>
+        <v>63.512</v>
       </c>
       <c r="E9" t="n">
-        <v>67.194</v>
+        <v>67.214</v>
       </c>
       <c r="F9" t="n">
-        <v>64.15300000000001</v>
+        <v>64.14100000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1160280</v>
+        <v>1160520</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>40.705</v>
+        <v>40.434</v>
       </c>
       <c r="E10" t="n">
-        <v>41.876</v>
+        <v>42.338</v>
       </c>
       <c r="F10" t="n">
-        <v>40.771</v>
+        <v>40.59</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1160520</v>
+        <v>1160610</v>
       </c>
     </row>
     <row r="11">
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>554.77</v>
+        <v>567.45</v>
       </c>
       <c r="E11" t="n">
-        <v>563.467</v>
+        <v>581.937</v>
       </c>
       <c r="F11" t="n">
-        <v>554.712</v>
+        <v>569.104</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5048400</v>
+        <v>5045370</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>489.635</v>
+        <v>488.805</v>
       </c>
       <c r="E12" t="n">
-        <v>513.102</v>
+        <v>510.691</v>
       </c>
       <c r="F12" t="n">
-        <v>492.871</v>
+        <v>493.048</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>477.902</v>
+        <v>474.075</v>
       </c>
       <c r="E13" t="n">
-        <v>506.108</v>
+        <v>490.27</v>
       </c>
       <c r="F13" t="n">
-        <v>482.014</v>
+        <v>476.195</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>411.024</v>
+        <v>402.466</v>
       </c>
       <c r="E14" t="n">
-        <v>420.021</v>
+        <v>425.895</v>
       </c>
       <c r="F14" t="n">
-        <v>412.102</v>
+        <v>405.718</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1043.416</v>
+        <v>1055.114</v>
       </c>
       <c r="E15" t="n">
-        <v>1069.192</v>
+        <v>1077.591</v>
       </c>
       <c r="F15" t="n">
-        <v>1045.385</v>
+        <v>1058.02</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>720.1660000000001</v>
+        <v>710.011</v>
       </c>
       <c r="E16" t="n">
-        <v>741.549</v>
+        <v>774.6900000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>722.984</v>
+        <v>718.787</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>599.582</v>
+        <v>602.8819999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>630.758</v>
+        <v>620.847</v>
       </c>
       <c r="F17" t="n">
-        <v>603.755</v>
+        <v>604.328</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>863.325</v>
+        <v>851.095</v>
       </c>
       <c r="E18" t="n">
-        <v>871.831</v>
+        <v>872.297</v>
       </c>
       <c r="F18" t="n">
-        <v>829.942</v>
+        <v>854.329</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>471.481</v>
+        <v>470.786</v>
       </c>
       <c r="E19" t="n">
-        <v>481.848</v>
+        <v>480.189</v>
       </c>
       <c r="F19" t="n">
-        <v>472.639</v>
+        <v>472.085</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>453.844</v>
+        <v>488.788</v>
       </c>
       <c r="E20" t="n">
-        <v>469.714</v>
+        <v>506.121</v>
       </c>
       <c r="F20" t="n">
-        <v>455.228</v>
+        <v>491.301</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>719.9109999999999</v>
+        <v>722.187</v>
       </c>
       <c r="E21" t="n">
-        <v>742.092</v>
+        <v>758.212</v>
       </c>
       <c r="F21" t="n">
-        <v>722.961</v>
+        <v>702.394</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>39.831</v>
+        <v>7.578</v>
       </c>
       <c r="E22" t="n">
-        <v>42.551</v>
+        <v>8.238</v>
       </c>
       <c r="F22" t="n">
-        <v>40.1</v>
+        <v>7.661</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1160730</v>
+        <v>548580</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>53.359</v>
+        <v>9.308999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>56.113</v>
+        <v>10.776</v>
       </c>
       <c r="F23" t="n">
-        <v>53.84</v>
+        <v>9.446</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1152030</v>
+        <v>548040</v>
       </c>
     </row>
     <row r="24">
@@ -1145,19 +1145,19 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.054</v>
+        <v>0.053</v>
       </c>
       <c r="E24" t="n">
-        <v>0.081</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.057</v>
+        <v>0.056</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25">
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>224.516</v>
+        <v>582.591</v>
       </c>
       <c r="E25" t="n">
-        <v>234.457</v>
+        <v>620.366</v>
       </c>
       <c r="F25" t="n">
-        <v>225.897</v>
+        <v>588.645</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1568400</v>
+        <v>167490</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>65.032</v>
+        <v>15.079</v>
       </c>
       <c r="E26" t="n">
-        <v>66.727</v>
+        <v>15.532</v>
       </c>
       <c r="F26" t="n">
-        <v>65.274</v>
+        <v>15.183</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1282740</v>
+        <v>1221540</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>102.162</v>
+        <v>100.7</v>
       </c>
       <c r="E27" t="n">
-        <v>126.878</v>
+        <v>104.72</v>
       </c>
       <c r="F27" t="n">
-        <v>105.944</v>
+        <v>101.107</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1435890</v>
+        <v>1433130</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>433.247</v>
+        <v>409.811</v>
       </c>
       <c r="E28" t="n">
-        <v>452.388</v>
+        <v>449.235</v>
       </c>
       <c r="F28" t="n">
-        <v>435.992</v>
+        <v>415.426</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>53.933</v>
+        <v>7.325</v>
       </c>
       <c r="E29" t="n">
-        <v>55.467</v>
+        <v>9.159000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>54.072</v>
+        <v>7.523</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1154520</v>
+        <v>548100</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>50.642</v>
+        <v>8.675000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>56.406</v>
+        <v>9.667</v>
       </c>
       <c r="F30" t="n">
-        <v>52.26</v>
+        <v>8.473000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1154490</v>
+        <v>548040</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>313.826</v>
+        <v>207.984</v>
       </c>
       <c r="E31" t="n">
-        <v>323.985</v>
+        <v>220.328</v>
       </c>
       <c r="F31" t="n">
-        <v>314.315</v>
+        <v>209.579</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1548570</v>
+        <v>14319810</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>168.352</v>
+        <v>186.628</v>
       </c>
       <c r="E32" t="n">
-        <v>182.424</v>
+        <v>204.077</v>
       </c>
       <c r="F32" t="n">
-        <v>170.274</v>
+        <v>189.854</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>292.857</v>
+        <v>270.406</v>
       </c>
       <c r="E33" t="n">
-        <v>313.145</v>
+        <v>277.501</v>
       </c>
       <c r="F33" t="n">
-        <v>296.226</v>
+        <v>271.821</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>159.578</v>
+        <v>152.91</v>
       </c>
       <c r="E34" t="n">
-        <v>168.5</v>
+        <v>164.226</v>
       </c>
       <c r="F34" t="n">
-        <v>160.99</v>
+        <v>154.382</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>638.96</v>
+        <v>670.7910000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>670.526</v>
+        <v>730.001</v>
       </c>
       <c r="F35" t="n">
-        <v>641.42</v>
+        <v>676.414</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>183.382</v>
+        <v>168.252</v>
       </c>
       <c r="E36" t="n">
-        <v>230.664</v>
+        <v>203.165</v>
       </c>
       <c r="F36" t="n">
-        <v>191.445</v>
+        <v>171.984</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>340.09</v>
+        <v>324.517</v>
       </c>
       <c r="E37" t="n">
-        <v>384.87</v>
+        <v>355.284</v>
       </c>
       <c r="F37" t="n">
-        <v>351.465</v>
+        <v>329.541</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>453.914</v>
+        <v>427.599</v>
       </c>
       <c r="E38" t="n">
-        <v>491.039</v>
+        <v>451.296</v>
       </c>
       <c r="F38" t="n">
-        <v>458.022</v>
+        <v>432.278</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>238.012</v>
+        <v>249.631</v>
       </c>
       <c r="E39" t="n">
-        <v>280.246</v>
+        <v>268.555</v>
       </c>
       <c r="F39" t="n">
-        <v>244.599</v>
+        <v>253.586</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>307.154</v>
+        <v>285.459</v>
       </c>
       <c r="E40" t="n">
-        <v>323.534</v>
+        <v>296.812</v>
       </c>
       <c r="F40" t="n">
-        <v>309.884</v>
+        <v>286.47</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>325.346</v>
+        <v>311.835</v>
       </c>
       <c r="E41" t="n">
-        <v>338.206</v>
+        <v>327.621</v>
       </c>
       <c r="F41" t="n">
-        <v>326.356</v>
+        <v>312.64</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1548570</v>
+        <v>1548690</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_1000000.xlsx
+++ b/exports/performance_run_1000000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>48.954</v>
+        <v>51.479</v>
       </c>
       <c r="E2" t="n">
-        <v>51.938</v>
+        <v>56.692</v>
       </c>
       <c r="F2" t="n">
-        <v>49.489</v>
+        <v>52.178</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1165020</v>
+        <v>1165230</v>
       </c>
     </row>
     <row r="3">
@@ -515,19 +515,19 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>82.562</v>
+        <v>85.35299999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>84.27</v>
+        <v>90.583</v>
       </c>
       <c r="F3" t="n">
-        <v>82.67400000000001</v>
+        <v>86.169</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1154760</v>
+        <v>1155960</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="E4" t="n">
-        <v>0.076</v>
+        <v>0.083</v>
       </c>
       <c r="F4" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,19 +575,19 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>394.306</v>
+        <v>423.991</v>
       </c>
       <c r="E5" t="n">
-        <v>411.085</v>
+        <v>481.971</v>
       </c>
       <c r="F5" t="n">
-        <v>396.667</v>
+        <v>428.687</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5006220</v>
+        <v>5022300</v>
       </c>
     </row>
     <row r="6">
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>96.364</v>
+        <v>99.349</v>
       </c>
       <c r="E6" t="n">
-        <v>98.471</v>
+        <v>104.356</v>
       </c>
       <c r="F6" t="n">
-        <v>96.676</v>
+        <v>99.863</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2086500</v>
+        <v>2101860</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>220.744</v>
+        <v>227.985</v>
       </c>
       <c r="E7" t="n">
-        <v>231.107</v>
+        <v>233.497</v>
       </c>
       <c r="F7" t="n">
-        <v>222.163</v>
+        <v>228.268</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2730450</v>
+        <v>2736000</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>873.7859999999999</v>
+        <v>886.052</v>
       </c>
       <c r="E8" t="n">
-        <v>900.72</v>
+        <v>947.967</v>
       </c>
       <c r="F8" t="n">
-        <v>877.5839999999999</v>
+        <v>889.592</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>63.512</v>
+        <v>63.931</v>
       </c>
       <c r="E9" t="n">
-        <v>67.214</v>
+        <v>67.587</v>
       </c>
       <c r="F9" t="n">
-        <v>64.14100000000001</v>
+        <v>64.381</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1160520</v>
+        <v>1167360</v>
       </c>
     </row>
     <row r="10">
@@ -725,13 +725,13 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>40.434</v>
+        <v>41.209</v>
       </c>
       <c r="E10" t="n">
-        <v>42.338</v>
+        <v>42.824</v>
       </c>
       <c r="F10" t="n">
-        <v>40.59</v>
+        <v>41.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -755,19 +755,19 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>567.45</v>
+        <v>560.294</v>
       </c>
       <c r="E11" t="n">
-        <v>581.937</v>
+        <v>576.604</v>
       </c>
       <c r="F11" t="n">
-        <v>569.104</v>
+        <v>562.619</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5045370</v>
+        <v>5155770</v>
       </c>
     </row>
     <row r="12">
@@ -785,19 +785,19 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>488.805</v>
+        <v>489.809</v>
       </c>
       <c r="E12" t="n">
-        <v>510.691</v>
+        <v>532.427</v>
       </c>
       <c r="F12" t="n">
-        <v>493.048</v>
+        <v>495.195</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4990170</v>
+        <v>9980340</v>
       </c>
     </row>
     <row r="13">
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>474.075</v>
+        <v>486.109</v>
       </c>
       <c r="E13" t="n">
-        <v>490.27</v>
+        <v>504.63</v>
       </c>
       <c r="F13" t="n">
-        <v>476.195</v>
+        <v>487.1</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>402.466</v>
+        <v>415.01</v>
       </c>
       <c r="E14" t="n">
-        <v>425.895</v>
+        <v>433.829</v>
       </c>
       <c r="F14" t="n">
-        <v>405.718</v>
+        <v>415.208</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1055.114</v>
+        <v>1034.082</v>
       </c>
       <c r="E15" t="n">
-        <v>1077.591</v>
+        <v>1054.908</v>
       </c>
       <c r="F15" t="n">
-        <v>1058.02</v>
+        <v>1034.104</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>710.011</v>
+        <v>740.8099999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>774.6900000000001</v>
+        <v>771.111</v>
       </c>
       <c r="F16" t="n">
-        <v>718.787</v>
+        <v>742.057</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>602.8819999999999</v>
+        <v>630.372</v>
       </c>
       <c r="E17" t="n">
-        <v>620.847</v>
+        <v>643.139</v>
       </c>
       <c r="F17" t="n">
-        <v>604.328</v>
+        <v>628.821</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>851.095</v>
+        <v>874.921</v>
       </c>
       <c r="E18" t="n">
-        <v>872.297</v>
+        <v>1031.622</v>
       </c>
       <c r="F18" t="n">
-        <v>854.329</v>
+        <v>903.651</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>470.786</v>
+        <v>471.948</v>
       </c>
       <c r="E19" t="n">
-        <v>480.189</v>
+        <v>485.372</v>
       </c>
       <c r="F19" t="n">
-        <v>472.085</v>
+        <v>474.339</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>488.788</v>
+        <v>490.102</v>
       </c>
       <c r="E20" t="n">
-        <v>506.121</v>
+        <v>501.909</v>
       </c>
       <c r="F20" t="n">
-        <v>491.301</v>
+        <v>491.614</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>722.187</v>
+        <v>731.9059999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>758.212</v>
+        <v>749.494</v>
       </c>
       <c r="F21" t="n">
-        <v>702.394</v>
+        <v>734.49</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>7.578</v>
+        <v>7.49</v>
       </c>
       <c r="E22" t="n">
-        <v>8.238</v>
+        <v>8.146000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>7.661</v>
+        <v>7.61</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>548580</v>
+        <v>538290</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>9.308999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>10.776</v>
+        <v>11.224</v>
       </c>
       <c r="F23" t="n">
-        <v>9.446</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>548040</v>
+        <v>548580</v>
       </c>
     </row>
     <row r="24">
@@ -1145,19 +1145,19 @@
         <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>0.053</v>
+        <v>0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="F24" t="n">
-        <v>0.056</v>
+        <v>0.044</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>360</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25">
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>582.591</v>
+        <v>584.636</v>
       </c>
       <c r="E25" t="n">
-        <v>620.366</v>
+        <v>605.52</v>
       </c>
       <c r="F25" t="n">
-        <v>588.645</v>
+        <v>587.143</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>167490</v>
+        <v>113400</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>15.079</v>
+        <v>14.856</v>
       </c>
       <c r="E26" t="n">
-        <v>15.532</v>
+        <v>16.359</v>
       </c>
       <c r="F26" t="n">
-        <v>15.183</v>
+        <v>14.994</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1221540</v>
+        <v>1199160</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>100.7</v>
+        <v>105.221</v>
       </c>
       <c r="E27" t="n">
-        <v>104.72</v>
+        <v>114.575</v>
       </c>
       <c r="F27" t="n">
-        <v>101.107</v>
+        <v>106.428</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1433130</v>
+        <v>1437990</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>409.811</v>
+        <v>423.994</v>
       </c>
       <c r="E28" t="n">
-        <v>449.235</v>
+        <v>554.009</v>
       </c>
       <c r="F28" t="n">
-        <v>415.426</v>
+        <v>447.608</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>7.325</v>
+        <v>7.09</v>
       </c>
       <c r="E29" t="n">
-        <v>9.159000000000001</v>
+        <v>8.515000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>7.523</v>
+        <v>7.274</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>548100</v>
+        <v>548640</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>8.675000000000001</v>
+        <v>7.148</v>
       </c>
       <c r="E30" t="n">
-        <v>9.667</v>
+        <v>8.5</v>
       </c>
       <c r="F30" t="n">
-        <v>8.473000000000001</v>
+        <v>7.277</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>548040</v>
+        <v>548580</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>207.984</v>
+        <v>216.686</v>
       </c>
       <c r="E31" t="n">
-        <v>220.328</v>
+        <v>245.581</v>
       </c>
       <c r="F31" t="n">
-        <v>209.579</v>
+        <v>217.327</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>14319810</v>
+        <v>14160270</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>186.628</v>
+        <v>186.726</v>
       </c>
       <c r="E32" t="n">
-        <v>204.077</v>
+        <v>192.508</v>
       </c>
       <c r="F32" t="n">
-        <v>189.854</v>
+        <v>187.361</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1548690</v>
+        <v>3097020</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>270.406</v>
+        <v>271.699</v>
       </c>
       <c r="E33" t="n">
-        <v>277.501</v>
+        <v>281.347</v>
       </c>
       <c r="F33" t="n">
-        <v>271.821</v>
+        <v>264.373</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>152.91</v>
+        <v>159.365</v>
       </c>
       <c r="E34" t="n">
-        <v>164.226</v>
+        <v>170.618</v>
       </c>
       <c r="F34" t="n">
-        <v>154.382</v>
+        <v>159.674</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>670.7910000000001</v>
+        <v>689.141</v>
       </c>
       <c r="E35" t="n">
-        <v>730.001</v>
+        <v>750.436</v>
       </c>
       <c r="F35" t="n">
-        <v>676.414</v>
+        <v>692.467</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>168.252</v>
+        <v>171.021</v>
       </c>
       <c r="E36" t="n">
-        <v>203.165</v>
+        <v>195.309</v>
       </c>
       <c r="F36" t="n">
-        <v>171.984</v>
+        <v>176.912</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>324.517</v>
+        <v>373.313</v>
       </c>
       <c r="E37" t="n">
-        <v>355.284</v>
+        <v>456.006</v>
       </c>
       <c r="F37" t="n">
-        <v>329.541</v>
+        <v>375.148</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>427.599</v>
+        <v>422.737</v>
       </c>
       <c r="E38" t="n">
-        <v>451.296</v>
+        <v>459.885</v>
       </c>
       <c r="F38" t="n">
-        <v>432.278</v>
+        <v>429.475</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>249.631</v>
+        <v>249.269</v>
       </c>
       <c r="E39" t="n">
-        <v>268.555</v>
+        <v>264.596</v>
       </c>
       <c r="F39" t="n">
-        <v>253.586</v>
+        <v>252.099</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>285.459</v>
+        <v>287.538</v>
       </c>
       <c r="E40" t="n">
-        <v>296.812</v>
+        <v>303.428</v>
       </c>
       <c r="F40" t="n">
-        <v>286.47</v>
+        <v>289.328</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>311.835</v>
+        <v>322.962</v>
       </c>
       <c r="E41" t="n">
-        <v>327.621</v>
+        <v>328.661</v>
       </c>
       <c r="F41" t="n">
-        <v>312.64</v>
+        <v>321.41</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1548690</v>
+        <v>1548510</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_1000000.xlsx
+++ b/exports/performance_run_1000000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>51.479</v>
+        <v>49.987</v>
       </c>
       <c r="E2" t="n">
-        <v>56.692</v>
+        <v>51.633</v>
       </c>
       <c r="F2" t="n">
-        <v>52.178</v>
+        <v>50.143</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1165230</v>
+        <v>1164810</v>
       </c>
     </row>
     <row r="3">
@@ -515,13 +515,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>85.35299999999999</v>
+        <v>86.851</v>
       </c>
       <c r="E3" t="n">
-        <v>90.583</v>
+        <v>90.121</v>
       </c>
       <c r="F3" t="n">
-        <v>86.169</v>
+        <v>87.163</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="E4" t="n">
-        <v>0.083</v>
+        <v>0.063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>423.991</v>
+        <v>358.158</v>
       </c>
       <c r="E5" t="n">
-        <v>481.971</v>
+        <v>469.178</v>
       </c>
       <c r="F5" t="n">
-        <v>428.687</v>
+        <v>384.606</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>99.349</v>
+        <v>98.355</v>
       </c>
       <c r="E6" t="n">
-        <v>104.356</v>
+        <v>101.285</v>
       </c>
       <c r="F6" t="n">
-        <v>99.863</v>
+        <v>98.979</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2101860</v>
+        <v>2106180</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>227.985</v>
+        <v>226.155</v>
       </c>
       <c r="E7" t="n">
-        <v>233.497</v>
+        <v>234.301</v>
       </c>
       <c r="F7" t="n">
-        <v>228.268</v>
+        <v>227.142</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2736000</v>
+        <v>2736030</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>886.052</v>
+        <v>881.928</v>
       </c>
       <c r="E8" t="n">
-        <v>947.967</v>
+        <v>897.2380000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>889.592</v>
+        <v>881.7089999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>63.931</v>
+        <v>64.63200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>67.587</v>
+        <v>68.16800000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>64.381</v>
+        <v>65.215</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1167360</v>
+        <v>1167960</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>41.209</v>
+        <v>41.198</v>
       </c>
       <c r="E10" t="n">
-        <v>42.824</v>
+        <v>43.171</v>
       </c>
       <c r="F10" t="n">
-        <v>41.5</v>
+        <v>41.474</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1160610</v>
+        <v>1160940</v>
       </c>
     </row>
     <row r="11">
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>560.294</v>
+        <v>578.297</v>
       </c>
       <c r="E11" t="n">
-        <v>576.604</v>
+        <v>592.229</v>
       </c>
       <c r="F11" t="n">
-        <v>562.619</v>
+        <v>579.7140000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>489.809</v>
+        <v>494.908</v>
       </c>
       <c r="E12" t="n">
-        <v>532.427</v>
+        <v>502.622</v>
       </c>
       <c r="F12" t="n">
-        <v>495.195</v>
+        <v>495.576</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>486.109</v>
+        <v>487.047</v>
       </c>
       <c r="E13" t="n">
-        <v>504.63</v>
+        <v>492.481</v>
       </c>
       <c r="F13" t="n">
-        <v>487.1</v>
+        <v>486.713</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>415.01</v>
+        <v>423.125</v>
       </c>
       <c r="E14" t="n">
-        <v>433.829</v>
+        <v>432.024</v>
       </c>
       <c r="F14" t="n">
-        <v>415.208</v>
+        <v>422.844</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1034.082</v>
+        <v>1047.283</v>
       </c>
       <c r="E15" t="n">
-        <v>1054.908</v>
+        <v>1080.176</v>
       </c>
       <c r="F15" t="n">
-        <v>1034.104</v>
+        <v>1040.884</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>740.8099999999999</v>
+        <v>729.314</v>
       </c>
       <c r="E16" t="n">
-        <v>771.111</v>
+        <v>741.205</v>
       </c>
       <c r="F16" t="n">
-        <v>742.057</v>
+        <v>727.395</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>630.372</v>
+        <v>612.301</v>
       </c>
       <c r="E17" t="n">
-        <v>643.139</v>
+        <v>631.823</v>
       </c>
       <c r="F17" t="n">
-        <v>628.821</v>
+        <v>613.266</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>874.921</v>
+        <v>861.2140000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1031.622</v>
+        <v>874.8339999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>903.651</v>
+        <v>861.974</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>471.948</v>
+        <v>471.92</v>
       </c>
       <c r="E19" t="n">
-        <v>485.372</v>
+        <v>484.347</v>
       </c>
       <c r="F19" t="n">
-        <v>474.339</v>
+        <v>474.755</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>490.102</v>
+        <v>496.651</v>
       </c>
       <c r="E20" t="n">
-        <v>501.909</v>
+        <v>509.841</v>
       </c>
       <c r="F20" t="n">
-        <v>491.614</v>
+        <v>497.943</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>731.9059999999999</v>
+        <v>732.234</v>
       </c>
       <c r="E21" t="n">
-        <v>749.494</v>
+        <v>749.035</v>
       </c>
       <c r="F21" t="n">
-        <v>734.49</v>
+        <v>732.006</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>7.49</v>
+        <v>8.114000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>8.146000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>7.61</v>
+        <v>8.627000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>538290</v>
+        <v>540900</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>9.529999999999999</v>
+        <v>9.734999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>11.224</v>
+        <v>12.497</v>
       </c>
       <c r="F23" t="n">
-        <v>9.710000000000001</v>
+        <v>10.268</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>548580</v>
+        <v>540750</v>
       </c>
     </row>
     <row r="24">
@@ -1148,10 +1148,10 @@
         <v>0.042</v>
       </c>
       <c r="E24" t="n">
-        <v>0.062</v>
+        <v>0.044</v>
       </c>
       <c r="F24" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,19 +1175,19 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>584.636</v>
+        <v>608.593</v>
       </c>
       <c r="E25" t="n">
-        <v>605.52</v>
+        <v>644.121</v>
       </c>
       <c r="F25" t="n">
-        <v>587.143</v>
+        <v>613.272</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>113400</v>
+        <v>113280</v>
       </c>
     </row>
     <row r="26">
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>14.856</v>
+        <v>15.545</v>
       </c>
       <c r="E26" t="n">
-        <v>16.359</v>
+        <v>16.905</v>
       </c>
       <c r="F26" t="n">
-        <v>14.994</v>
+        <v>15.732</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1199160</v>
+        <v>1194630</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>105.221</v>
+        <v>103.307</v>
       </c>
       <c r="E27" t="n">
-        <v>114.575</v>
+        <v>104.658</v>
       </c>
       <c r="F27" t="n">
-        <v>106.428</v>
+        <v>103.424</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1437990</v>
+        <v>1437630</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>423.994</v>
+        <v>418.444</v>
       </c>
       <c r="E28" t="n">
-        <v>554.009</v>
+        <v>453.491</v>
       </c>
       <c r="F28" t="n">
-        <v>447.608</v>
+        <v>423.433</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>7.09</v>
+        <v>7.254</v>
       </c>
       <c r="E29" t="n">
-        <v>8.515000000000001</v>
+        <v>10.891</v>
       </c>
       <c r="F29" t="n">
-        <v>7.274</v>
+        <v>7.943</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>548640</v>
+        <v>540810</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>7.148</v>
+        <v>7.528</v>
       </c>
       <c r="E30" t="n">
-        <v>8.5</v>
+        <v>7.876</v>
       </c>
       <c r="F30" t="n">
-        <v>7.277</v>
+        <v>7.626</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>548580</v>
+        <v>540750</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>216.686</v>
+        <v>212.867</v>
       </c>
       <c r="E31" t="n">
-        <v>245.581</v>
+        <v>236.833</v>
       </c>
       <c r="F31" t="n">
-        <v>217.327</v>
+        <v>217.921</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>14160270</v>
+        <v>14124480</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>186.726</v>
+        <v>189.163</v>
       </c>
       <c r="E32" t="n">
-        <v>192.508</v>
+        <v>208.69</v>
       </c>
       <c r="F32" t="n">
-        <v>187.361</v>
+        <v>192.776</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3097020</v>
+        <v>3096780</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>271.699</v>
+        <v>281.119</v>
       </c>
       <c r="E33" t="n">
-        <v>281.347</v>
+        <v>287.622</v>
       </c>
       <c r="F33" t="n">
-        <v>264.373</v>
+        <v>281.372</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>159.365</v>
+        <v>163.482</v>
       </c>
       <c r="E34" t="n">
-        <v>170.618</v>
+        <v>184.804</v>
       </c>
       <c r="F34" t="n">
-        <v>159.674</v>
+        <v>166.747</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>689.141</v>
+        <v>686.965</v>
       </c>
       <c r="E35" t="n">
-        <v>750.436</v>
+        <v>751.399</v>
       </c>
       <c r="F35" t="n">
-        <v>692.467</v>
+        <v>693.248</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>171.021</v>
+        <v>169.143</v>
       </c>
       <c r="E36" t="n">
-        <v>195.309</v>
+        <v>181.294</v>
       </c>
       <c r="F36" t="n">
-        <v>176.912</v>
+        <v>170.452</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>373.313</v>
+        <v>338.656</v>
       </c>
       <c r="E37" t="n">
-        <v>456.006</v>
+        <v>369.14</v>
       </c>
       <c r="F37" t="n">
-        <v>375.148</v>
+        <v>343.618</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>422.737</v>
+        <v>434.805</v>
       </c>
       <c r="E38" t="n">
-        <v>459.885</v>
+        <v>471.155</v>
       </c>
       <c r="F38" t="n">
-        <v>429.475</v>
+        <v>438.959</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>249.269</v>
+        <v>251.41</v>
       </c>
       <c r="E39" t="n">
-        <v>264.596</v>
+        <v>263.143</v>
       </c>
       <c r="F39" t="n">
-        <v>252.099</v>
+        <v>253.398</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>287.538</v>
+        <v>291.303</v>
       </c>
       <c r="E40" t="n">
-        <v>303.428</v>
+        <v>307.094</v>
       </c>
       <c r="F40" t="n">
-        <v>289.328</v>
+        <v>291.569</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>322.962</v>
+        <v>313.222</v>
       </c>
       <c r="E41" t="n">
-        <v>328.661</v>
+        <v>321.828</v>
       </c>
       <c r="F41" t="n">
-        <v>321.41</v>
+        <v>313.794</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1548510</v>
+        <v>1548390</v>
       </c>
     </row>
   </sheetData>

--- a/exports/performance_run_1000000.xlsx
+++ b/exports/performance_run_1000000.xlsx
@@ -485,19 +485,19 @@
         <v>30</v>
       </c>
       <c r="D2" t="n">
-        <v>49.987</v>
+        <v>49.723</v>
       </c>
       <c r="E2" t="n">
-        <v>51.633</v>
+        <v>51.998</v>
       </c>
       <c r="F2" t="n">
-        <v>50.143</v>
+        <v>50.014</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1164810</v>
+        <v>1164720</v>
       </c>
     </row>
     <row r="3">
@@ -515,13 +515,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>86.851</v>
+        <v>86.247</v>
       </c>
       <c r="E3" t="n">
-        <v>90.121</v>
+        <v>95.69</v>
       </c>
       <c r="F3" t="n">
-        <v>87.163</v>
+        <v>89.20399999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -545,13 +545,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="E4" t="n">
         <v>0.063</v>
       </c>
       <c r="F4" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -575,13 +575,13 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>358.158</v>
+        <v>409.208</v>
       </c>
       <c r="E5" t="n">
-        <v>469.178</v>
+        <v>477.865</v>
       </c>
       <c r="F5" t="n">
-        <v>384.606</v>
+        <v>416.839</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>98.355</v>
+        <v>95.67</v>
       </c>
       <c r="E6" t="n">
-        <v>101.285</v>
+        <v>99.34</v>
       </c>
       <c r="F6" t="n">
-        <v>98.979</v>
+        <v>96.304</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2106180</v>
+        <v>2104620</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +635,19 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>226.155</v>
+        <v>221.467</v>
       </c>
       <c r="E7" t="n">
-        <v>234.301</v>
+        <v>227.468</v>
       </c>
       <c r="F7" t="n">
-        <v>227.142</v>
+        <v>221.715</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>2736030</v>
+        <v>2735880</v>
       </c>
     </row>
     <row r="8">
@@ -665,13 +665,13 @@
         <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>881.928</v>
+        <v>869.7859999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>897.2380000000001</v>
+        <v>906.028</v>
       </c>
       <c r="F8" t="n">
-        <v>881.7089999999999</v>
+        <v>875.8</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -695,19 +695,19 @@
         <v>30</v>
       </c>
       <c r="D9" t="n">
-        <v>64.63200000000001</v>
+        <v>63.57</v>
       </c>
       <c r="E9" t="n">
-        <v>68.16800000000001</v>
+        <v>66.88200000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>65.215</v>
+        <v>63.965</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1167960</v>
+        <v>1167180</v>
       </c>
     </row>
     <row r="10">
@@ -725,19 +725,19 @@
         <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>41.198</v>
+        <v>39.873</v>
       </c>
       <c r="E10" t="n">
-        <v>43.171</v>
+        <v>41.336</v>
       </c>
       <c r="F10" t="n">
-        <v>41.474</v>
+        <v>40.107</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1160940</v>
+        <v>1160550</v>
       </c>
     </row>
     <row r="11">
@@ -755,13 +755,13 @@
         <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>578.297</v>
+        <v>565.183</v>
       </c>
       <c r="E11" t="n">
-        <v>592.229</v>
+        <v>590.768</v>
       </c>
       <c r="F11" t="n">
-        <v>579.7140000000001</v>
+        <v>569.912</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -785,13 +785,13 @@
         <v>30</v>
       </c>
       <c r="D12" t="n">
-        <v>494.908</v>
+        <v>488.024</v>
       </c>
       <c r="E12" t="n">
-        <v>502.622</v>
+        <v>500.51</v>
       </c>
       <c r="F12" t="n">
-        <v>495.576</v>
+        <v>490.659</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,13 +815,13 @@
         <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>487.047</v>
+        <v>493.408</v>
       </c>
       <c r="E13" t="n">
-        <v>492.481</v>
+        <v>542.351</v>
       </c>
       <c r="F13" t="n">
-        <v>486.713</v>
+        <v>497.474</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -845,13 +845,13 @@
         <v>30</v>
       </c>
       <c r="D14" t="n">
-        <v>423.125</v>
+        <v>410.783</v>
       </c>
       <c r="E14" t="n">
-        <v>432.024</v>
+        <v>458.588</v>
       </c>
       <c r="F14" t="n">
-        <v>422.844</v>
+        <v>417.446</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>1047.283</v>
+        <v>1121.846</v>
       </c>
       <c r="E15" t="n">
-        <v>1080.176</v>
+        <v>1195.449</v>
       </c>
       <c r="F15" t="n">
-        <v>1040.884</v>
+        <v>1116.561</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -905,13 +905,13 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>729.314</v>
+        <v>709.651</v>
       </c>
       <c r="E16" t="n">
-        <v>741.205</v>
+        <v>746.41</v>
       </c>
       <c r="F16" t="n">
-        <v>727.395</v>
+        <v>715.698</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -935,13 +935,13 @@
         <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>612.301</v>
+        <v>598.054</v>
       </c>
       <c r="E17" t="n">
-        <v>631.823</v>
+        <v>619.22</v>
       </c>
       <c r="F17" t="n">
-        <v>613.266</v>
+        <v>600.136</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -965,13 +965,13 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>861.2140000000001</v>
+        <v>849.557</v>
       </c>
       <c r="E18" t="n">
-        <v>874.8339999999999</v>
+        <v>875.158</v>
       </c>
       <c r="F18" t="n">
-        <v>861.974</v>
+        <v>852.793</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -995,13 +995,13 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>471.92</v>
+        <v>464.901</v>
       </c>
       <c r="E19" t="n">
-        <v>484.347</v>
+        <v>484.896</v>
       </c>
       <c r="F19" t="n">
-        <v>474.755</v>
+        <v>467.265</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1025,13 +1025,13 @@
         <v>30</v>
       </c>
       <c r="D20" t="n">
-        <v>496.651</v>
+        <v>484.091</v>
       </c>
       <c r="E20" t="n">
-        <v>509.841</v>
+        <v>518.154</v>
       </c>
       <c r="F20" t="n">
-        <v>497.943</v>
+        <v>489.387</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>30</v>
       </c>
       <c r="D21" t="n">
-        <v>732.234</v>
+        <v>722.129</v>
       </c>
       <c r="E21" t="n">
-        <v>749.035</v>
+        <v>741.2910000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>732.006</v>
+        <v>724.837</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1085,19 +1085,19 @@
         <v>30</v>
       </c>
       <c r="D22" t="n">
-        <v>8.114000000000001</v>
+        <v>7.379</v>
       </c>
       <c r="E22" t="n">
-        <v>9.880000000000001</v>
+        <v>7.551</v>
       </c>
       <c r="F22" t="n">
-        <v>8.627000000000001</v>
+        <v>7.428</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>540900</v>
+        <v>542550</v>
       </c>
     </row>
     <row r="23">
@@ -1115,19 +1115,19 @@
         <v>30</v>
       </c>
       <c r="D23" t="n">
-        <v>9.734999999999999</v>
+        <v>10.03</v>
       </c>
       <c r="E23" t="n">
-        <v>12.497</v>
+        <v>12.226</v>
       </c>
       <c r="F23" t="n">
-        <v>10.268</v>
+        <v>10.711</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>540750</v>
+        <v>544410</v>
       </c>
     </row>
     <row r="24">
@@ -1148,10 +1148,10 @@
         <v>0.042</v>
       </c>
       <c r="E24" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="F24" t="n">
         <v>0.044</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.042</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>608.593</v>
+        <v>591.925</v>
       </c>
       <c r="E25" t="n">
-        <v>644.121</v>
+        <v>623.966</v>
       </c>
       <c r="F25" t="n">
-        <v>613.272</v>
+        <v>596.514</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1205,19 +1205,19 @@
         <v>30</v>
       </c>
       <c r="D26" t="n">
-        <v>15.545</v>
+        <v>15.398</v>
       </c>
       <c r="E26" t="n">
-        <v>16.905</v>
+        <v>17.866</v>
       </c>
       <c r="F26" t="n">
-        <v>15.732</v>
+        <v>15.627</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1194630</v>
+        <v>1191240</v>
       </c>
     </row>
     <row r="27">
@@ -1235,19 +1235,19 @@
         <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>103.307</v>
+        <v>99.72</v>
       </c>
       <c r="E27" t="n">
-        <v>104.658</v>
+        <v>103.013</v>
       </c>
       <c r="F27" t="n">
-        <v>103.424</v>
+        <v>100.175</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1437630</v>
+        <v>1437240</v>
       </c>
     </row>
     <row r="28">
@@ -1265,19 +1265,19 @@
         <v>30</v>
       </c>
       <c r="D28" t="n">
-        <v>418.444</v>
+        <v>405.72</v>
       </c>
       <c r="E28" t="n">
-        <v>453.491</v>
+        <v>447.552</v>
       </c>
       <c r="F28" t="n">
-        <v>423.433</v>
+        <v>415.569</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="29">
@@ -1295,19 +1295,19 @@
         <v>30</v>
       </c>
       <c r="D29" t="n">
-        <v>7.254</v>
+        <v>6.97</v>
       </c>
       <c r="E29" t="n">
-        <v>10.891</v>
+        <v>8.516</v>
       </c>
       <c r="F29" t="n">
-        <v>7.943</v>
+        <v>7.15</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>540810</v>
+        <v>544410</v>
       </c>
     </row>
     <row r="30">
@@ -1325,19 +1325,19 @@
         <v>30</v>
       </c>
       <c r="D30" t="n">
-        <v>7.528</v>
+        <v>7.318</v>
       </c>
       <c r="E30" t="n">
-        <v>7.876</v>
+        <v>9.095000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>7.626</v>
+        <v>7.832</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>540750</v>
+        <v>544410</v>
       </c>
     </row>
     <row r="31">
@@ -1355,19 +1355,19 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>212.867</v>
+        <v>204.436</v>
       </c>
       <c r="E31" t="n">
-        <v>236.833</v>
+        <v>213.118</v>
       </c>
       <c r="F31" t="n">
-        <v>217.921</v>
+        <v>205.666</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>14124480</v>
+        <v>14141760</v>
       </c>
     </row>
     <row r="32">
@@ -1385,19 +1385,19 @@
         <v>30</v>
       </c>
       <c r="D32" t="n">
-        <v>189.163</v>
+        <v>187.773</v>
       </c>
       <c r="E32" t="n">
-        <v>208.69</v>
+        <v>200.05</v>
       </c>
       <c r="F32" t="n">
-        <v>192.776</v>
+        <v>189.312</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3096780</v>
+        <v>3097080</v>
       </c>
     </row>
     <row r="33">
@@ -1415,19 +1415,19 @@
         <v>30</v>
       </c>
       <c r="D33" t="n">
-        <v>281.119</v>
+        <v>292.182</v>
       </c>
       <c r="E33" t="n">
-        <v>287.622</v>
+        <v>329.692</v>
       </c>
       <c r="F33" t="n">
-        <v>281.372</v>
+        <v>292.712</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="34">
@@ -1445,19 +1445,19 @@
         <v>30</v>
       </c>
       <c r="D34" t="n">
-        <v>163.482</v>
+        <v>163.521</v>
       </c>
       <c r="E34" t="n">
-        <v>184.804</v>
+        <v>188.317</v>
       </c>
       <c r="F34" t="n">
-        <v>166.747</v>
+        <v>167.875</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="35">
@@ -1475,19 +1475,19 @@
         <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>686.965</v>
+        <v>736.3440000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>751.399</v>
+        <v>868.443</v>
       </c>
       <c r="F35" t="n">
-        <v>693.248</v>
+        <v>762.129</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="36">
@@ -1505,19 +1505,19 @@
         <v>30</v>
       </c>
       <c r="D36" t="n">
-        <v>169.143</v>
+        <v>162.722</v>
       </c>
       <c r="E36" t="n">
-        <v>181.294</v>
+        <v>207.183</v>
       </c>
       <c r="F36" t="n">
-        <v>170.452</v>
+        <v>171.188</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="37">
@@ -1535,19 +1535,19 @@
         <v>30</v>
       </c>
       <c r="D37" t="n">
-        <v>338.656</v>
+        <v>314.451</v>
       </c>
       <c r="E37" t="n">
-        <v>369.14</v>
+        <v>342.797</v>
       </c>
       <c r="F37" t="n">
-        <v>343.618</v>
+        <v>320.016</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="38">
@@ -1565,19 +1565,19 @@
         <v>30</v>
       </c>
       <c r="D38" t="n">
-        <v>434.805</v>
+        <v>430.872</v>
       </c>
       <c r="E38" t="n">
-        <v>471.155</v>
+        <v>491.311</v>
       </c>
       <c r="F38" t="n">
-        <v>438.959</v>
+        <v>441.459</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="39">
@@ -1595,19 +1595,19 @@
         <v>30</v>
       </c>
       <c r="D39" t="n">
-        <v>251.41</v>
+        <v>248.519</v>
       </c>
       <c r="E39" t="n">
-        <v>263.143</v>
+        <v>258.803</v>
       </c>
       <c r="F39" t="n">
-        <v>253.398</v>
+        <v>250.92</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="40">
@@ -1625,19 +1625,19 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>291.303</v>
+        <v>284.063</v>
       </c>
       <c r="E40" t="n">
-        <v>307.094</v>
+        <v>297.759</v>
       </c>
       <c r="F40" t="n">
-        <v>291.569</v>
+        <v>286.004</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
     <row r="41">
@@ -1655,19 +1655,19 @@
         <v>30</v>
       </c>
       <c r="D41" t="n">
-        <v>313.222</v>
+        <v>305.505</v>
       </c>
       <c r="E41" t="n">
-        <v>321.828</v>
+        <v>313.949</v>
       </c>
       <c r="F41" t="n">
-        <v>313.794</v>
+        <v>305.698</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1548390</v>
+        <v>1548540</v>
       </c>
     </row>
   </sheetData>
